--- a/dataset/construct/dataset_splits/data_size/20_percent/merged/fold3.xlsx
+++ b/dataset/construct/dataset_splits/data_size/20_percent/merged/fold3.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN37"/>
+  <dimension ref="A1:AK37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,185 +446,170 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>DM</t>
+          <t>BMI</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>BMI</t>
+          <t>AFPRE</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>CABGPRE</t>
+          <t>LVEFPRE</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>AFPRE</t>
+          <t>PREDILATION</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>LVEFPRE</t>
+          <t>CT_ValScNCC</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>NTPROBNPPRE</t>
+          <t>CT_ValScRCC</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>PREDILATION</t>
+          <t>CT_ValScLCC</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScNCC</t>
+          <t>CT_ValvScTot</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScRCC</t>
+          <t>CT_AnnScNCC</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScLCC</t>
+          <t>CT_AnnScRCC</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValvScTot</t>
+          <t>CT_AnnScLCC</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScNCC</t>
+          <t>CT_AnnScTot</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScRCC</t>
+          <t>CT_LVOTScNCC</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScLCC</t>
+          <t>CT_LVOTScRCC</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScTot</t>
+          <t>CT_LVOTScLCC</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScNCC</t>
+          <t>CT_LVOTScTot</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScRCC</t>
+          <t>SEX</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScLCC</t>
+          <t>CT_AnnMean</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScTot</t>
+          <t>ECC_INDEX</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>SEX</t>
+          <t>CT_Peri_Deri</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnMean</t>
+          <t>CT_Area_Deri</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>ECC_INDEX</t>
+          <t>nyha2</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>CT_Peri_Deri</t>
+          <t>nyha3</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>CT_Area_Deri</t>
+          <t>nyha4</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>nyha2</t>
+          <t>model1</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>nyha3</t>
+          <t>model2</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>nyha4</t>
+          <t>model3</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>model1</t>
+          <t>model4</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>model2</t>
+          <t>model7</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>model3</t>
+          <t>model8</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>model4</t>
+          <t>brand2</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>model7</t>
+          <t>brand8</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>model8</t>
+          <t>QRSADM</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>brand2</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>brand8</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>QRSADM</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>PQADM</t>
         </is>
@@ -632,7 +617,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>662</v>
+        <v>344</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -640,123 +625,114 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>82.8652711232793</v>
+        <v>85.91221886328491</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>25.8805706350208</v>
       </c>
       <c r="E2" t="n">
-        <v>26.0422405876951</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>50</v>
+        <v>432</v>
       </c>
       <c r="I2" t="n">
-        <v>10800</v>
+        <v>378</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>203</v>
       </c>
       <c r="K2" t="n">
-        <v>169</v>
+        <v>1013</v>
       </c>
       <c r="L2" t="n">
-        <v>515</v>
+        <v>52</v>
       </c>
       <c r="M2" t="n">
-        <v>306</v>
+        <v>37</v>
       </c>
       <c r="N2" t="n">
-        <v>990</v>
+        <v>16</v>
       </c>
       <c r="O2" t="n">
-        <v>27</v>
+        <v>105</v>
       </c>
       <c r="P2" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="Q2" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>78</v>
+        <v>2</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>29.3</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>28.9661319073084</v>
       </c>
       <c r="X2" t="n">
-        <v>25.1</v>
+        <v>28.6082260699118</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.154411764705882</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>25.4647313470843</v>
+        <v>1</v>
       </c>
       <c r="AA2" t="n">
-        <v>25.0500676016111</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AK2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>86</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>184</v>
+        <v>254</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>579</v>
+        <v>519</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -764,79 +740,79 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>79.1056030876873</v>
+        <v>77.5943455776105</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>34.2058298631766</v>
       </c>
       <c r="E3" t="n">
-        <v>25.390625</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>50</v>
+        <v>376.3</v>
       </c>
       <c r="I3" t="n">
-        <v>5640</v>
+        <v>275.7</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>276.5</v>
       </c>
       <c r="K3" t="n">
-        <v>282</v>
+        <v>928.5</v>
       </c>
       <c r="L3" t="n">
-        <v>283</v>
+        <v>25.6</v>
       </c>
       <c r="M3" t="n">
-        <v>266</v>
+        <v>33.7</v>
       </c>
       <c r="N3" t="n">
-        <v>831</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>158</v>
+        <v>123.9</v>
       </c>
       <c r="P3" t="n">
-        <v>41</v>
+        <v>22.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>276</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>17</v>
+        <v>22.9</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>24.55</v>
       </c>
       <c r="V3" t="n">
-        <v>17</v>
+        <v>0.19</v>
       </c>
       <c r="W3" t="n">
-        <v>2</v>
+        <v>24.859943977591</v>
       </c>
       <c r="X3" t="n">
-        <v>24.4</v>
+        <v>24.5496573149696</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.281690140845071</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>24.5098039215686</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>23.8260951566085</v>
+        <v>1</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
@@ -845,7 +821,7 @@
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
         <v>0</v>
@@ -863,24 +839,13 @@
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>146</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="AK3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1962</v>
+        <v>2013</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -888,79 +853,79 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>74.1123504322255</v>
+        <v>92.0309740284432</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>26.7949380165289</v>
       </c>
       <c r="E4" t="n">
-        <v>25.0593070266296</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>30</v>
+        <v>262.3</v>
       </c>
       <c r="I4" t="n">
-        <v>35000</v>
+        <v>377.1</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>280.3</v>
       </c>
       <c r="K4" t="n">
-        <v>783.1</v>
+        <v>919.7</v>
       </c>
       <c r="L4" t="n">
-        <v>744.9</v>
+        <v>7.6</v>
       </c>
       <c r="M4" t="n">
-        <v>169</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1697</v>
+        <v>29.1</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4</v>
+        <v>36.7</v>
       </c>
       <c r="P4" t="n">
-        <v>196.2</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>196.6</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>92.3</v>
+        <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>24.6</v>
       </c>
       <c r="V4" t="n">
-        <v>92.3</v>
+        <v>0.12</v>
       </c>
       <c r="W4" t="n">
-        <v>1</v>
+        <v>24.5098039215686</v>
       </c>
       <c r="X4" t="n">
-        <v>28.15</v>
+        <v>26.4561900936673</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.19551282051282</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>28.5841609371021</v>
+        <v>1</v>
       </c>
       <c r="AA4" t="n">
-        <v>28.1846427181971</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -981,30 +946,19 @@
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>142</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>156</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="AK4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>336</v>
+        <v>1025</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1012,80 +966,82 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>83.0155395213831</v>
+        <v>85.2467825500038</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>30.3460743801652</v>
       </c>
       <c r="E5" t="n">
-        <v>19.7231833910034</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>20</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
+        <v>242.8</v>
+      </c>
+      <c r="I5" t="n">
+        <v>371.3</v>
+      </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>285.3</v>
       </c>
       <c r="K5" t="n">
-        <v>652</v>
+        <v>899.4000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>918</v>
+        <v>72.3</v>
       </c>
       <c r="M5" t="n">
-        <v>547</v>
+        <v>106.7</v>
       </c>
       <c r="N5" t="n">
-        <v>2117</v>
+        <v>85.3</v>
       </c>
       <c r="O5" t="n">
-        <v>95</v>
+        <v>264.3</v>
       </c>
       <c r="P5" t="n">
-        <v>157</v>
+        <v>22.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>344</v>
+        <v>53.2</v>
       </c>
       <c r="S5" t="n">
-        <v>32</v>
+        <v>75.80000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>88</v>
+        <v>26.9</v>
       </c>
       <c r="V5" t="n">
-        <v>142</v>
+        <v>0.16</v>
       </c>
       <c r="W5" t="n">
-        <v>1</v>
+        <v>27.1836007130125</v>
       </c>
       <c r="X5" t="n">
-        <v>26.4</v>
+        <v>26.8217134966894</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.204081632653061</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>27.0562770562771</v>
+        <v>1</v>
       </c>
       <c r="AA5" t="n">
-        <v>26.6741965227618</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1094,7 +1050,7 @@
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -1109,24 +1065,13 @@
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>162</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>186</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="AK5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2006</v>
+        <v>2319</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1134,85 +1079,85 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>67.10314342662311</v>
+        <v>77.2493207024615</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>28.515625</v>
       </c>
       <c r="E6" t="n">
-        <v>33.8123415046491</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>60</v>
+        <v>55.8</v>
       </c>
       <c r="I6" t="n">
-        <v>391</v>
+        <v>46.7</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>14.9</v>
       </c>
       <c r="K6" t="n">
-        <v>718.6</v>
+        <v>117.4</v>
       </c>
       <c r="L6" t="n">
-        <v>1023.4</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>535.8</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2277.8</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>140.7</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>59.7</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>252.4</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>100.6</v>
+        <v>2</v>
       </c>
       <c r="U6" t="n">
-        <v>5</v>
+        <v>22.8</v>
       </c>
       <c r="V6" t="n">
-        <v>105.6</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>22.5362872421696</v>
       </c>
       <c r="X6" t="n">
-        <v>27.2</v>
+        <v>22.1741916431478</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0912280701754387</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>27.6610644257703</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>27.3480481672903</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1221,36 +1166,27 @@
         <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="AK6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>92</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>226</v>
+        <v>190</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1258,85 +1194,85 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>86.0683245874211</v>
+        <v>74.1720111795574</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>25.9515570934256</v>
       </c>
       <c r="E7" t="n">
-        <v>21.484375</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>60</v>
+        <v>190</v>
       </c>
       <c r="I7" t="n">
-        <v>882</v>
+        <v>215</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>152</v>
       </c>
       <c r="K7" t="n">
-        <v>153</v>
+        <v>557</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>153</v>
+        <v>11</v>
       </c>
       <c r="O7" t="n">
+        <v>68</v>
+      </c>
+      <c r="P7" t="n">
         <v>49</v>
       </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
         <v>49</v>
       </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>22.9</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="n">
-        <v>2</v>
+        <v>22.5999490705373</v>
       </c>
       <c r="X7" t="n">
-        <v>19.8</v>
+        <v>22.3940969210825</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.255506607929515</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>20.690094219506</v>
+        <v>1</v>
       </c>
       <c r="AA7" t="n">
-        <v>20.1186577456453</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
@@ -1345,36 +1281,27 @@
         <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AK7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>78</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>182</v>
+        <v>160</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>696</v>
+        <v>2093</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1382,85 +1309,85 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>78.7061113329277</v>
+        <v>84.1487284521003</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>29.0174471992653</v>
       </c>
       <c r="E8" t="n">
-        <v>28.1969212010364</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>60</v>
+        <v>489.6</v>
       </c>
       <c r="I8" t="n">
-        <v>4960</v>
+        <v>405.5</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>217.9</v>
       </c>
       <c r="K8" t="n">
-        <v>842.5</v>
+        <v>1113</v>
       </c>
       <c r="L8" t="n">
-        <v>476.1</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>627.6</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1946.2</v>
+        <v>15.1</v>
       </c>
       <c r="O8" t="n">
-        <v>110.9</v>
+        <v>15.1</v>
       </c>
       <c r="P8" t="n">
-        <v>79.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>219.1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>409.9</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>39.4</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>57.7</v>
+        <v>23.95</v>
       </c>
       <c r="V8" t="n">
-        <v>97.09999999999999</v>
+        <v>0.35</v>
       </c>
       <c r="W8" t="n">
-        <v>2</v>
+        <v>23.9686783804431</v>
       </c>
       <c r="X8" t="n">
-        <v>24.3</v>
+        <v>22.9720679092787</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.206642066420664</v>
+        <v>1</v>
       </c>
       <c r="Z8" t="n">
-        <v>24.2551566080978</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>23.9911309690755</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
@@ -1469,7 +1396,7 @@
         <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
@@ -1481,24 +1408,15 @@
         <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>166</v>
+        <v>204</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>323</v>
+        <v>546</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1506,83 +1424,85 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>79.7188668339798</v>
+        <v>83.8833922731767</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>33.0904223676383</v>
       </c>
       <c r="E9" t="n">
-        <v>28.0403781445281</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>55</v>
-      </c>
-      <c r="I9" t="inlineStr"/>
+        <v>205</v>
+      </c>
+      <c r="I9" t="n">
+        <v>29</v>
+      </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>188</v>
       </c>
       <c r="K9" t="n">
-        <v>209</v>
+        <v>422</v>
       </c>
       <c r="L9" t="n">
-        <v>137.7</v>
+        <v>37</v>
       </c>
       <c r="M9" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>431.7</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q9" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>50</v>
+        <v>22.1</v>
       </c>
       <c r="V9" t="n">
-        <v>50</v>
+        <v>0.39</v>
       </c>
       <c r="W9" t="n">
-        <v>2</v>
+        <v>22.9182582123759</v>
       </c>
       <c r="X9" t="n">
-        <v>22.1</v>
+        <v>21.7452723622298</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.350746268656717</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>22.5999490705373</v>
+        <v>1</v>
       </c>
       <c r="AA9" t="n">
-        <v>21.406057760656</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -1594,33 +1514,22 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>103</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>140</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="AK9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1205</v>
+        <v>551</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1628,123 +1537,114 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>77.3262297196238</v>
+        <v>86.878606738155</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>23.1481481481481</v>
       </c>
       <c r="E10" t="n">
-        <v>21.09375</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>60</v>
+        <v>852</v>
       </c>
       <c r="I10" t="n">
-        <v>1550</v>
+        <v>377</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>892</v>
       </c>
       <c r="K10" t="n">
-        <v>242</v>
+        <v>2121</v>
       </c>
       <c r="L10" t="n">
-        <v>26</v>
+        <v>300</v>
       </c>
       <c r="M10" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="N10" t="n">
-        <v>308</v>
+        <v>204</v>
       </c>
       <c r="O10" t="n">
-        <v>37</v>
+        <v>552</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>37</v>
+        <v>204</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>474</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>23.7</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W10" t="n">
-        <v>2</v>
+        <v>23.8731856378915</v>
       </c>
       <c r="X10" t="n">
-        <v>20.8</v>
+        <v>23.5033791921504</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.15929203539823</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>21.3267125031831</v>
+        <v>1</v>
       </c>
       <c r="AA10" t="n">
-        <v>20.8945249963572</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>180</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>299</v>
+        <v>600</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1752,77 +1652,79 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>75.3335159517834</v>
+        <v>87.4373393413948</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>24.4444444444444</v>
       </c>
       <c r="E11" t="n">
-        <v>28.4567901234567</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>60</v>
-      </c>
-      <c r="I11" t="inlineStr"/>
+        <v>480</v>
+      </c>
+      <c r="I11" t="n">
+        <v>127</v>
+      </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>134</v>
       </c>
       <c r="K11" t="n">
-        <v>455</v>
+        <v>741</v>
       </c>
       <c r="L11" t="n">
-        <v>56</v>
+        <v>200</v>
       </c>
       <c r="M11" t="n">
-        <v>118</v>
+        <v>15</v>
       </c>
       <c r="N11" t="n">
-        <v>629</v>
+        <v>21</v>
       </c>
       <c r="O11" t="n">
-        <v>130</v>
+        <v>236</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>86</v>
+        <v>55</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="V11" t="n">
-        <v>86</v>
+        <v>0.21</v>
       </c>
       <c r="W11" t="n">
-        <v>1</v>
+        <v>20.2762923351159</v>
       </c>
       <c r="X11" t="n">
-        <v>26.3</v>
+        <v>19.9151768367782</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.258278145695364</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>27.6928953399542</v>
+        <v>1</v>
       </c>
       <c r="AA11" t="n">
-        <v>26.8406888888731</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
         <v>0</v>
@@ -1843,30 +1745,21 @@
         <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AK11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>98</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>212</v>
+        <v>190</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>53982483</v>
+        <v>54798778</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1874,74 +1767,80 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>83.37303216974681</v>
-      </c>
-      <c r="D12" t="inlineStr"/>
+        <v>84.1998631074606</v>
+      </c>
+      <c r="D12" t="n">
+        <v>20.4444444444444</v>
+      </c>
       <c r="E12" t="n">
-        <v>24.7720967102656</v>
-      </c>
-      <c r="F12" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>55</v>
+      </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
-      <c r="H12" t="n">
-        <v>31</v>
-      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="L12" t="n">
+        <v>80</v>
+      </c>
+      <c r="M12" t="n">
+        <v>8</v>
+      </c>
+      <c r="N12" t="n">
+        <v>27</v>
+      </c>
       <c r="O12" t="n">
-        <v>56</v>
+        <v>115</v>
       </c>
       <c r="P12" t="n">
-        <v>180</v>
+        <v>41</v>
       </c>
       <c r="Q12" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>297</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>20.7</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="W12" t="n">
-        <v>1</v>
+        <v>20.69014260194639</v>
       </c>
       <c r="X12" t="n">
-        <v>25.6</v>
+        <v>20.21972348511376</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>80.7</v>
+        <v>1</v>
       </c>
       <c r="AA12" t="n">
-        <v>499.5</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -1950,29 +1849,24 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
         <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>182</v>
       </c>
       <c r="AK12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM12" t="inlineStr"/>
-      <c r="AN12" t="inlineStr"/>
+        <v>93</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>54964291</v>
+        <v>53539217</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1980,74 +1874,88 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>77.10882956878849</v>
-      </c>
-      <c r="D13" t="inlineStr"/>
+        <v>85.23750855578371</v>
+      </c>
+      <c r="D13" t="n">
+        <v>27.8876170655567</v>
+      </c>
       <c r="E13" t="n">
-        <v>23.1206235962478</v>
-      </c>
-      <c r="F13" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>50</v>
+      </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>55</v>
-      </c>
-      <c r="I13" t="inlineStr"/>
+        <v>433</v>
+      </c>
+      <c r="I13" t="n">
+        <v>512</v>
+      </c>
       <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+        <v>286</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1231</v>
+      </c>
+      <c r="L13" t="n">
+        <v>356</v>
+      </c>
+      <c r="M13" t="n">
+        <v>416</v>
+      </c>
+      <c r="N13" t="n">
+        <v>246</v>
+      </c>
       <c r="O13" t="n">
-        <v>717</v>
+        <v>1018</v>
       </c>
       <c r="P13" t="n">
-        <v>173</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>189</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1079</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U13" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="V13" t="n">
-        <v>47</v>
+        <v>0.17</v>
       </c>
       <c r="W13" t="n">
-        <v>1</v>
+        <v>26.48338253049139</v>
       </c>
       <c r="X13" t="n">
-        <v>22.7</v>
+        <v>26.03354393206056</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>78.09999999999999</v>
+        <v>1</v>
       </c>
       <c r="AA13" t="n">
-        <v>406.7</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -2065,20 +1973,15 @@
         <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>187</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM13" t="inlineStr"/>
-      <c r="AN13" t="inlineStr"/>
+        <v>146</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>51212898</v>
+        <v>51721443</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -2086,84 +1989,86 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>70.8966461327858</v>
+        <v>83.8685831622177</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>26.4721074380165</v>
       </c>
       <c r="E14" t="n">
-        <v>27.7388544139095</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
         <v>1</v>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
+      <c r="H14" t="n">
+        <v>910</v>
+      </c>
+      <c r="I14" t="n">
+        <v>581</v>
+      </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>808</v>
       </c>
       <c r="K14" t="n">
-        <v>943</v>
+        <v>2299</v>
       </c>
       <c r="L14" t="n">
-        <v>899</v>
+        <v>910</v>
       </c>
       <c r="M14" t="n">
-        <v>860</v>
+        <v>431</v>
       </c>
       <c r="N14" t="n">
-        <v>2702</v>
+        <v>677</v>
       </c>
       <c r="O14" t="n">
-        <v>781</v>
+        <v>2018</v>
       </c>
       <c r="P14" t="n">
-        <v>894</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>843</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2518</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>227</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>29.5</v>
       </c>
       <c r="V14" t="n">
-        <v>297</v>
+        <v>0.25</v>
       </c>
       <c r="W14" t="n">
-        <v>1</v>
+        <v>29.76197435818443</v>
       </c>
       <c r="X14" t="n">
-        <v>25.4</v>
+        <v>28.71719438115369</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>82</v>
+        <v>1</v>
       </c>
       <c r="AA14" t="n">
-        <v>501.6</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -2181,20 +2086,15 @@
         <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="AK14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM14" t="inlineStr"/>
-      <c r="AN14" t="inlineStr"/>
+        <v>150</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>51202411</v>
+        <v>53291409</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -2202,83 +2102,85 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>81.6892539356605</v>
+        <v>81.79329226557149</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="E15" t="n">
-        <v>25.5036157024793</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
+        <v>310</v>
+      </c>
+      <c r="I15" t="n">
+        <v>66</v>
+      </c>
+      <c r="J15" t="n">
+        <v>63</v>
+      </c>
+      <c r="K15" t="n">
+        <v>439</v>
+      </c>
+      <c r="L15" t="n">
+        <v>310</v>
+      </c>
+      <c r="M15" t="n">
         <v>60</v>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>437</v>
-      </c>
-      <c r="L15" t="n">
-        <v>248</v>
-      </c>
-      <c r="M15" t="n">
-        <v>365</v>
-      </c>
       <c r="N15" t="n">
-        <v>1051</v>
+        <v>55</v>
       </c>
       <c r="O15" t="n">
-        <v>366</v>
+        <v>425</v>
       </c>
       <c r="P15" t="n">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>324</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>931</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>23.1</v>
       </c>
       <c r="V15" t="n">
-        <v>53</v>
+        <v>0.34</v>
       </c>
       <c r="W15" t="n">
-        <v>1</v>
+        <v>23.58676256621889</v>
       </c>
       <c r="X15" t="n">
-        <v>25.2</v>
+        <v>22.48279562821002</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>80.40000000000001</v>
+        <v>1</v>
       </c>
       <c r="AA15" t="n">
-        <v>485.5</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
         <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -2287,7 +2189,7 @@
         <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>
@@ -2296,27 +2198,14 @@
         <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>152</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>142</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>54555930</v>
+        <v>55006864</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -2324,109 +2213,106 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>87.2224503764545</v>
-      </c>
-      <c r="D16" t="inlineStr"/>
+        <v>81.80150581793291</v>
+      </c>
+      <c r="D16" t="n">
+        <v>22.4712087637714</v>
+      </c>
       <c r="E16" t="n">
-        <v>23.4375</v>
-      </c>
-      <c r="F16" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>45</v>
+      </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
-      <c r="H16" t="n">
-        <v>55</v>
-      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="L16" t="n">
+        <v>200</v>
+      </c>
+      <c r="M16" t="n">
+        <v>275</v>
+      </c>
+      <c r="N16" t="n">
+        <v>213</v>
+      </c>
       <c r="O16" t="n">
-        <v>445</v>
+        <v>688</v>
       </c>
       <c r="P16" t="n">
-        <v>196</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>304</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>944</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>170</v>
+        <v>27.2</v>
       </c>
       <c r="V16" t="n">
-        <v>176</v>
+        <v>0.21</v>
       </c>
       <c r="W16" t="n">
-        <v>1</v>
+        <v>27.15183329147735</v>
       </c>
       <c r="X16" t="n">
-        <v>24.6</v>
+        <v>26.68801606198651</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.29</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>78.5</v>
+        <v>1</v>
       </c>
       <c r="AA16" t="n">
-        <v>468.7</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
         <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="AK16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>186</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>156</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>53683397</v>
+        <v>52902100</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -2434,84 +2320,88 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>82.2149212867899</v>
+        <v>73.8507871321013</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>15.7557508490599</v>
       </c>
       <c r="E17" t="n">
-        <v>27.0538027739674</v>
-      </c>
-      <c r="F17" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>35</v>
+      </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>55</v>
-      </c>
-      <c r="I17" t="inlineStr"/>
+        <v>466</v>
+      </c>
+      <c r="I17" t="n">
+        <v>422</v>
+      </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>250</v>
       </c>
       <c r="K17" t="n">
-        <v>457</v>
+        <v>1138</v>
       </c>
       <c r="L17" t="n">
-        <v>187</v>
+        <v>466</v>
       </c>
       <c r="M17" t="n">
-        <v>138</v>
+        <v>336</v>
       </c>
       <c r="N17" t="n">
-        <v>781</v>
+        <v>109</v>
       </c>
       <c r="O17" t="n">
-        <v>457</v>
+        <v>911</v>
       </c>
       <c r="P17" t="n">
-        <v>187</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>138</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>781</v>
+        <v>27</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>24.6</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="W17" t="n">
-        <v>2</v>
+        <v>24.89183309957243</v>
       </c>
       <c r="X17" t="n">
-        <v>24.1</v>
+        <v>23.95514689606678</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>79.8</v>
+        <v>1</v>
       </c>
       <c r="AA17" t="n">
-        <v>463.9</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -2520,33 +2410,24 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>159</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>52070077</v>
+        <v>54382606</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -2554,80 +2435,80 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>87.04996577686521</v>
-      </c>
-      <c r="D18" t="inlineStr"/>
+        <v>80.2162902121834</v>
+      </c>
+      <c r="D18" t="n">
+        <v>32.5618850880572</v>
+      </c>
       <c r="E18" t="n">
-        <v>23.1111111111111</v>
-      </c>
-      <c r="F18" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>55</v>
+      </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>136</v>
-      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
-        <v>125</v>
+        <v>384</v>
       </c>
       <c r="M18" t="n">
-        <v>301</v>
+        <v>140</v>
       </c>
       <c r="N18" t="n">
-        <v>563</v>
+        <v>516</v>
       </c>
       <c r="O18" t="n">
-        <v>237</v>
+        <v>1040</v>
       </c>
       <c r="P18" t="n">
-        <v>168</v>
+        <v>3</v>
       </c>
       <c r="Q18" t="n">
-        <v>506</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>911</v>
+        <v>181</v>
       </c>
       <c r="S18" t="n">
-        <v>353</v>
+        <v>184</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>1649</v>
+        <v>25.1</v>
       </c>
       <c r="V18" t="n">
-        <v>2001</v>
+        <v>0.19</v>
       </c>
       <c r="W18" t="n">
-        <v>2</v>
+        <v>25.33746694022974</v>
       </c>
       <c r="X18" t="n">
-        <v>26</v>
+        <v>24.48088751877352</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>82.7</v>
+        <v>1</v>
       </c>
       <c r="AA18" t="n">
-        <v>499.8</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -2636,33 +2517,24 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>172</v>
       </c>
       <c r="AK18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>190</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>98</v>
+        <v>120</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>51672408</v>
+        <v>52859114</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -2670,73 +2542,79 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>88.6461327857632</v>
-      </c>
-      <c r="D19" t="inlineStr"/>
+        <v>86.425735797399</v>
+      </c>
+      <c r="D19" t="n">
+        <v>24.2214532871972</v>
+      </c>
       <c r="E19" t="n">
-        <v>24.4472789115646</v>
-      </c>
-      <c r="F19" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>60</v>
+      </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>53</v>
-      </c>
-      <c r="I19" t="inlineStr"/>
+        <v>178</v>
+      </c>
+      <c r="I19" t="n">
+        <v>100</v>
+      </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>142</v>
       </c>
       <c r="K19" t="n">
-        <v>199</v>
+        <v>420</v>
       </c>
       <c r="L19" t="n">
-        <v>339</v>
+        <v>178</v>
       </c>
       <c r="M19" t="n">
-        <v>433</v>
+        <v>63</v>
       </c>
       <c r="N19" t="n">
-        <v>972</v>
+        <v>127</v>
       </c>
       <c r="O19" t="n">
-        <v>167</v>
+        <v>368</v>
       </c>
       <c r="P19" t="n">
-        <v>252</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>305</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>724</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>297</v>
+        <v>23.1</v>
       </c>
       <c r="V19" t="n">
-        <v>443</v>
+        <v>0.3</v>
       </c>
       <c r="W19" t="n">
-        <v>1</v>
+        <v>23.84141047516592</v>
       </c>
       <c r="X19" t="n">
-        <v>29.8</v>
+        <v>22.96189224508361</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>96.2</v>
+        <v>1</v>
       </c>
       <c r="AA19" t="n">
-        <v>707.3</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
@@ -2754,33 +2632,24 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>166</v>
       </c>
       <c r="AK19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>164</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>140</v>
+        <v>117</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>54014281</v>
+        <v>55677933</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -2788,68 +2657,74 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>84.3148528405202</v>
-      </c>
-      <c r="D20" t="inlineStr"/>
+        <v>64.0684462696783</v>
+      </c>
+      <c r="D20" t="n">
+        <v>22.8350098277257</v>
+      </c>
       <c r="E20" t="n">
-        <v>23.3234180638183</v>
-      </c>
-      <c r="F20" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>45</v>
+      </c>
       <c r="G20" t="n">
         <v>1</v>
       </c>
-      <c r="H20" t="n">
-        <v>46</v>
-      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+      <c r="L20" t="n">
+        <v>1525.3033</v>
+      </c>
+      <c r="M20" t="n">
+        <v>861.2494</v>
+      </c>
+      <c r="N20" t="n">
+        <v>585.2203</v>
+      </c>
       <c r="O20" t="n">
-        <v>128</v>
+        <v>2971.773</v>
       </c>
       <c r="P20" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>246</v>
+        <v>14</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>27.69318</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="W20" t="n">
-        <v>2</v>
+        <v>27.72586888388279</v>
       </c>
       <c r="X20" t="n">
-        <v>25.5</v>
+        <v>27.28485830729072</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.19</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>79.2</v>
+        <v>1</v>
       </c>
       <c r="AA20" t="n">
-        <v>479.7</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2858,39 +2733,30 @@
         <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF20" t="n">
         <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="AK20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>142</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>83</v>
+        <v>102</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>52402765</v>
+        <v>52234465</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -2898,77 +2764,77 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>83.6030116358658</v>
+        <v>74.5544147843943</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>23.5102040816327</v>
       </c>
       <c r="E21" t="n">
-        <v>25.6369171607114</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>52</v>
-      </c>
-      <c r="I21" t="inlineStr"/>
+        <v>535</v>
+      </c>
+      <c r="I21" t="n">
+        <v>119</v>
+      </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>296</v>
       </c>
       <c r="K21" t="n">
-        <v>267</v>
+        <v>950</v>
       </c>
       <c r="L21" t="n">
-        <v>208</v>
+        <v>535</v>
       </c>
       <c r="M21" t="n">
-        <v>29</v>
+        <v>119</v>
       </c>
       <c r="N21" t="n">
-        <v>505</v>
+        <v>296</v>
       </c>
       <c r="O21" t="n">
-        <v>267</v>
+        <v>950</v>
       </c>
       <c r="P21" t="n">
-        <v>208</v>
+        <v>78</v>
       </c>
       <c r="Q21" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>505</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>26.4</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="W21" t="n">
-        <v>2</v>
+        <v>26.32422758739949</v>
       </c>
       <c r="X21" t="n">
-        <v>24.5</v>
+        <v>25.89869865777977</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.19</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>76.7</v>
+        <v>1</v>
       </c>
       <c r="AA21" t="n">
-        <v>436</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -2977,7 +2843,7 @@
         <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -2994,25 +2860,12 @@
       <c r="AI21" t="n">
         <v>0</v>
       </c>
-      <c r="AJ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>122</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>135</v>
-      </c>
+      <c r="AJ21" t="inlineStr"/>
+      <c r="AK21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>55358586</v>
+        <v>54964291</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -3020,65 +2873,71 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>71.73169062286109</v>
-      </c>
-      <c r="D22" t="inlineStr"/>
+        <v>77.10882956878849</v>
+      </c>
+      <c r="D22" t="n">
+        <v>23.1206235962478</v>
+      </c>
       <c r="E22" t="n">
-        <v>41.7222393215006</v>
-      </c>
-      <c r="F22" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>55</v>
+      </c>
       <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>55</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="n">
-        <v>1</v>
-      </c>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+      <c r="L22" t="n">
+        <v>717</v>
+      </c>
+      <c r="M22" t="n">
+        <v>173</v>
+      </c>
+      <c r="N22" t="n">
+        <v>189</v>
+      </c>
       <c r="O22" t="n">
-        <v>334.4122</v>
+        <v>1079</v>
       </c>
       <c r="P22" t="n">
-        <v>147.0067</v>
+        <v>43</v>
       </c>
       <c r="Q22" t="n">
-        <v>346.91656</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>828.33545</v>
+        <v>3</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>22.7</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="W22" t="n">
-        <v>2</v>
+        <v>24.86000211095405</v>
       </c>
       <c r="X22" t="n">
-        <v>24.381985</v>
+        <v>22.75580196002309</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.09</v>
+        <v>1</v>
       </c>
       <c r="Z22" t="n">
-        <v>78.733604</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>468.17468</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
@@ -3090,10 +2949,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -3102,27 +2961,14 @@
         <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>187</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>146</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AJ22" t="inlineStr"/>
+      <c r="AK22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>55801460</v>
+        <v>52772610</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -3130,74 +2976,88 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>90.0150581793292</v>
-      </c>
-      <c r="D23" t="inlineStr"/>
+        <v>82.2313483915127</v>
+      </c>
+      <c r="D23" t="n">
+        <v>24.3417582863402</v>
+      </c>
       <c r="E23" t="n">
-        <v>22.8930740819877</v>
-      </c>
-      <c r="F23" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>35</v>
+      </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>40</v>
-      </c>
-      <c r="I23" t="inlineStr"/>
+        <v>622</v>
+      </c>
+      <c r="I23" t="n">
+        <v>632</v>
+      </c>
       <c r="J23" t="n">
-        <v>1</v>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+        <v>653</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1907</v>
+      </c>
+      <c r="L23" t="n">
+        <v>622</v>
+      </c>
+      <c r="M23" t="n">
+        <v>431</v>
+      </c>
+      <c r="N23" t="n">
+        <v>622</v>
+      </c>
       <c r="O23" t="n">
-        <v>208.14648</v>
+        <v>1675</v>
       </c>
       <c r="P23" t="n">
-        <v>142.76782</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>160.41797</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>511.33228</v>
+        <v>88</v>
       </c>
       <c r="S23" t="n">
-        <v>26</v>
+        <v>88</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>31.1</v>
       </c>
       <c r="V23" t="n">
-        <v>26</v>
+        <v>0.33</v>
       </c>
       <c r="W23" t="n">
-        <v>1</v>
+        <v>32.34028443627313</v>
       </c>
       <c r="X23" t="n">
-        <v>28.647072</v>
+        <v>30.52886088189566</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>90.27831999999999</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>615.0072</v>
+        <v>1</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
@@ -3214,25 +3074,12 @@
       <c r="AI23" t="n">
         <v>0</v>
       </c>
-      <c r="AJ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>137</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>163</v>
-      </c>
+      <c r="AJ23" t="inlineStr"/>
+      <c r="AK23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>51961920</v>
+        <v>51549417</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -3240,115 +3087,114 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>85.864476386037</v>
+        <v>69.864476386037</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>24.2122933884297</v>
       </c>
       <c r="E24" t="n">
-        <v>23.5555555555556</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
       </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
+      <c r="H24" t="n">
+        <v>781</v>
+      </c>
+      <c r="I24" t="n">
+        <v>641</v>
+      </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>735</v>
       </c>
       <c r="K24" t="n">
-        <v>456</v>
+        <v>2157</v>
       </c>
       <c r="L24" t="n">
-        <v>379</v>
+        <v>774</v>
       </c>
       <c r="M24" t="n">
-        <v>506</v>
+        <v>351</v>
       </c>
       <c r="N24" t="n">
-        <v>1341</v>
+        <v>595</v>
       </c>
       <c r="O24" t="n">
-        <v>392</v>
+        <v>1720</v>
       </c>
       <c r="P24" t="n">
-        <v>352</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>506</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1250</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>571</v>
+        <v>27</v>
       </c>
       <c r="V24" t="n">
-        <v>571</v>
+        <v>0.14</v>
       </c>
       <c r="W24" t="n">
-        <v>2</v>
+        <v>28.17042492726548</v>
       </c>
       <c r="X24" t="n">
-        <v>26.8</v>
+        <v>27.44305359669089</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.29</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>85</v>
+        <v>1</v>
       </c>
       <c r="AA24" t="n">
-        <v>534.4</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF24" t="n">
         <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
         <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>189</v>
       </c>
       <c r="AK24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM24" t="inlineStr"/>
-      <c r="AN24" t="inlineStr"/>
+        <v>153</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>52496143</v>
+        <v>53688310</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -3356,79 +3202,85 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>86.07802874743329</v>
-      </c>
-      <c r="D25" t="inlineStr"/>
+        <v>92.7775496235455</v>
+      </c>
+      <c r="D25" t="n">
+        <v>30.4498269896194</v>
+      </c>
       <c r="E25" t="n">
-        <v>23.1206235962478</v>
-      </c>
-      <c r="F25" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F25" t="n">
+        <v>50</v>
+      </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>60</v>
-      </c>
-      <c r="I25" t="inlineStr"/>
+        <v>683</v>
+      </c>
+      <c r="I25" t="n">
+        <v>643</v>
+      </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>414</v>
       </c>
       <c r="K25" t="n">
-        <v>298</v>
+        <v>1740</v>
       </c>
       <c r="L25" t="n">
-        <v>45</v>
+        <v>683</v>
       </c>
       <c r="M25" t="n">
-        <v>93</v>
+        <v>574</v>
       </c>
       <c r="N25" t="n">
-        <v>437</v>
+        <v>408</v>
       </c>
       <c r="O25" t="n">
-        <v>290</v>
+        <v>1665</v>
       </c>
       <c r="P25" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="Q25" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>428</v>
+        <v>11</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>26.5</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="W25" t="n">
-        <v>1</v>
+        <v>26.57887549634652</v>
       </c>
       <c r="X25" t="n">
-        <v>30.1</v>
+        <v>26.20416162512499</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>100.9</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>731.2</v>
+        <v>1</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
         <v>0</v>
@@ -3437,10 +3289,10 @@
         <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
         <v>0</v>
@@ -3448,25 +3300,12 @@
       <c r="AI25" t="n">
         <v>0</v>
       </c>
-      <c r="AJ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>166</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>152</v>
-      </c>
+      <c r="AJ25" t="inlineStr"/>
+      <c r="AK25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>51855783</v>
+        <v>54514630</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -3474,83 +3313,77 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>75.41957563312801</v>
+        <v>82.2915811088296</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>27.8851873884593</v>
       </c>
       <c r="E26" t="n">
-        <v>24.4265887509131</v>
+        <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
-      <c r="H26" t="n">
-        <v>43</v>
-      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="n">
-        <v>1</v>
-      </c>
-      <c r="K26" t="n">
-        <v>1077</v>
-      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="n">
-        <v>961</v>
+        <v>258</v>
       </c>
       <c r="M26" t="n">
-        <v>1198</v>
+        <v>84</v>
       </c>
       <c r="N26" t="n">
-        <v>3236</v>
+        <v>131</v>
       </c>
       <c r="O26" t="n">
-        <v>1077</v>
+        <v>473</v>
       </c>
       <c r="P26" t="n">
-        <v>864</v>
+        <v>33</v>
       </c>
       <c r="Q26" t="n">
-        <v>1198</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>3139</v>
+        <v>102</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="T26" t="n">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>460</v>
+        <v>23.5</v>
       </c>
       <c r="V26" t="n">
-        <v>530</v>
+        <v>0.22</v>
       </c>
       <c r="W26" t="n">
-        <v>1</v>
+        <v>24.06422739549457</v>
       </c>
       <c r="X26" t="n">
-        <v>28.4</v>
+        <v>23.49902105517675</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>96.90000000000001</v>
+        <v>1</v>
       </c>
       <c r="AA26" t="n">
-        <v>685</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD26" t="n">
         <v>0</v>
@@ -3571,24 +3404,15 @@
         <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="AK26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>192</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>149</v>
+        <v>112</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>51838049</v>
+        <v>55050615</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -3596,89 +3420,83 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>78.7132101300479</v>
+        <v>63.6659822039699</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>26.5949841287998</v>
       </c>
       <c r="E27" t="n">
-        <v>21.0480476121353</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="n">
-        <v>59</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="n">
-        <v>1</v>
-      </c>
-      <c r="K27" t="n">
-        <v>212</v>
-      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="n">
-        <v>130</v>
+        <v>263</v>
       </c>
       <c r="M27" t="n">
-        <v>14</v>
+        <v>922</v>
       </c>
       <c r="N27" t="n">
-        <v>356</v>
+        <v>251</v>
       </c>
       <c r="O27" t="n">
-        <v>212</v>
+        <v>1436</v>
       </c>
       <c r="P27" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="R27" t="n">
-        <v>312</v>
+        <v>20</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>30.1</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="W27" t="n">
-        <v>2</v>
+        <v>30.90788994844607</v>
       </c>
       <c r="X27" t="n">
-        <v>26.3</v>
+        <v>29.64439127012409</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="Z27" t="n">
-        <v>85.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>542.1</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF27" t="n">
         <v>0</v>
@@ -3687,30 +3505,21 @@
         <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>222</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>182</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>120</v>
+        <v>128</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>51602743</v>
+        <v>51409719</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -3718,86 +3527,88 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>87.21697467488021</v>
+        <v>76.2765229295003</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>29.3523545006944</v>
       </c>
       <c r="E28" t="n">
-        <v>19.1673469387755</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>47</v>
-      </c>
-      <c r="I28" t="inlineStr"/>
+        <v>527</v>
+      </c>
+      <c r="I28" t="n">
+        <v>702</v>
+      </c>
       <c r="J28" t="n">
-        <v>1</v>
+        <v>676</v>
       </c>
       <c r="K28" t="n">
-        <v>1055</v>
+        <v>1905</v>
       </c>
       <c r="L28" t="n">
-        <v>1016</v>
+        <v>485</v>
       </c>
       <c r="M28" t="n">
-        <v>938</v>
+        <v>252</v>
       </c>
       <c r="N28" t="n">
-        <v>3009</v>
+        <v>702</v>
       </c>
       <c r="O28" t="n">
-        <v>1018</v>
+        <v>1439</v>
       </c>
       <c r="P28" t="n">
-        <v>937</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>926</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>2881</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>83</v>
+        <v>25.9</v>
       </c>
       <c r="V28" t="n">
-        <v>119</v>
+        <v>0.22</v>
       </c>
       <c r="W28" t="n">
-        <v>1</v>
+        <v>26.96084735976707</v>
       </c>
       <c r="X28" t="n">
-        <v>31</v>
+        <v>26.15065887271783</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>98.59999999999999</v>
+        <v>1</v>
       </c>
       <c r="AA28" t="n">
-        <v>735.9</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -3815,20 +3626,15 @@
         <v>0</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="AK28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM28" t="inlineStr"/>
-      <c r="AN28" t="inlineStr"/>
+        <v>151</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>53283194</v>
+        <v>52251082</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -3836,84 +3642,88 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>84.30116358658449</v>
+        <v>78.0506502395619</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>25.8805706350208</v>
       </c>
       <c r="E29" t="n">
-        <v>29.296875</v>
-      </c>
-      <c r="F29" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F29" t="n">
+        <v>60</v>
+      </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>45</v>
-      </c>
-      <c r="I29" t="inlineStr"/>
+        <v>306</v>
+      </c>
+      <c r="I29" t="n">
+        <v>117</v>
+      </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>250</v>
       </c>
       <c r="K29" t="n">
-        <v>82</v>
+        <v>673</v>
       </c>
       <c r="L29" t="n">
-        <v>88</v>
+        <v>306</v>
       </c>
       <c r="M29" t="n">
-        <v>30</v>
+        <v>117</v>
       </c>
       <c r="N29" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="O29" t="n">
-        <v>82</v>
+        <v>673</v>
       </c>
       <c r="P29" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>25.4</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="W29" t="n">
-        <v>2</v>
+        <v>27.02450933700383</v>
       </c>
       <c r="X29" t="n">
-        <v>25</v>
+        <v>25.87656616663467</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>79</v>
+        <v>1</v>
       </c>
       <c r="AA29" t="n">
-        <v>469.7</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
         <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -3925,26 +3735,17 @@
         <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM29" t="inlineStr"/>
-      <c r="AN29" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr"/>
+      <c r="AK29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>52832940</v>
+        <v>54520442</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -3952,121 +3753,102 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>76.7556468172485</v>
+        <v>89.160848733744</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>28.8979591836735</v>
       </c>
       <c r="E30" t="n">
-        <v>23.5102040816327</v>
+        <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" t="n">
-        <v>66</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="n">
-        <v>1</v>
-      </c>
-      <c r="K30" t="n">
-        <v>561</v>
-      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="n">
-        <v>813</v>
+        <v>658</v>
       </c>
       <c r="M30" t="n">
-        <v>460</v>
+        <v>284</v>
       </c>
       <c r="N30" t="n">
-        <v>1834</v>
+        <v>367</v>
       </c>
       <c r="O30" t="n">
-        <v>540</v>
+        <v>1309</v>
       </c>
       <c r="P30" t="n">
-        <v>495</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>433</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1468</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>27.1</v>
       </c>
       <c r="V30" t="n">
-        <v>40</v>
+        <v>0.33</v>
       </c>
       <c r="W30" t="n">
-        <v>1</v>
+        <v>27.75662207522655</v>
       </c>
       <c r="X30" t="n">
-        <v>28.1</v>
+        <v>26.8165190669188</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>89.59999999999999</v>
+        <v>1</v>
       </c>
       <c r="AA30" t="n">
-        <v>604.5</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
         <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF30" t="n">
         <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
       </c>
-      <c r="AJ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>174</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>148</v>
-      </c>
+      <c r="AJ30" t="inlineStr"/>
+      <c r="AK30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>54603873</v>
+        <v>55489860</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -4074,68 +3856,74 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>77.5468856947296</v>
-      </c>
-      <c r="D31" t="inlineStr"/>
+        <v>86.73237508555781</v>
+      </c>
+      <c r="D31" t="n">
+        <v>27.6360544217687</v>
+      </c>
       <c r="E31" t="n">
-        <v>31.1791383219955</v>
-      </c>
-      <c r="F31" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>55</v>
+      </c>
       <c r="G31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" t="n">
-        <v>55</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+      <c r="L31" t="n">
+        <v>1294.7904</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1057.8282</v>
+      </c>
+      <c r="N31" t="n">
+        <v>895.4634</v>
+      </c>
       <c r="O31" t="n">
-        <v>170</v>
+        <v>3248.082</v>
       </c>
       <c r="P31" t="n">
-        <v>373</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>645</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>67</v>
+        <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>27.020199</v>
       </c>
       <c r="V31" t="n">
-        <v>67</v>
+        <v>0.19</v>
       </c>
       <c r="W31" t="n">
-        <v>1</v>
+        <v>27.79335185299329</v>
       </c>
       <c r="X31" t="n">
-        <v>26.9</v>
+        <v>27.23903219341589</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>85.2</v>
+        <v>1</v>
       </c>
       <c r="AA31" t="n">
-        <v>560.7</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4144,7 +3932,7 @@
         <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF31" t="n">
         <v>0</v>
@@ -4158,25 +3946,12 @@
       <c r="AI31" t="n">
         <v>0</v>
       </c>
-      <c r="AJ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>151</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>134</v>
-      </c>
+      <c r="AJ31" t="inlineStr"/>
+      <c r="AK31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>53531320</v>
+        <v>52010506</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -4184,119 +3959,110 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>82.072553045859</v>
+        <v>76.06297056810401</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>31.8877551020408</v>
       </c>
       <c r="E32" t="n">
-        <v>23.4375</v>
-      </c>
-      <c r="F32" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>55</v>
+      </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" t="n">
-        <v>45</v>
-      </c>
-      <c r="I32" t="inlineStr"/>
+        <v>418</v>
+      </c>
+      <c r="I32" t="n">
+        <v>172</v>
+      </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="K32" t="n">
-        <v>182</v>
+        <v>704</v>
       </c>
       <c r="L32" t="n">
-        <v>337</v>
+        <v>418</v>
       </c>
       <c r="M32" t="n">
-        <v>144</v>
+        <v>172</v>
       </c>
       <c r="N32" t="n">
-        <v>663</v>
+        <v>114</v>
       </c>
       <c r="O32" t="n">
-        <v>175</v>
+        <v>704</v>
       </c>
       <c r="P32" t="n">
-        <v>276</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>544</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>27.7</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="W32" t="n">
-        <v>2</v>
+        <v>29.5073264492374</v>
       </c>
       <c r="X32" t="n">
-        <v>24.8</v>
+        <v>27.92139991550101</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>81.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>486.8</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
         <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
       </c>
-      <c r="AJ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>144</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>136</v>
-      </c>
+      <c r="AJ32" t="inlineStr"/>
+      <c r="AK32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>53620694</v>
+        <v>55673806</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -4304,79 +4070,77 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>83.8740588637919</v>
-      </c>
-      <c r="D33" t="inlineStr"/>
+        <v>86.43942505133469</v>
+      </c>
+      <c r="D33" t="n">
+        <v>20.7756232686981</v>
+      </c>
       <c r="E33" t="n">
-        <v>25.5102040816327</v>
-      </c>
-      <c r="F33" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>50</v>
+      </c>
       <c r="G33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" t="n">
-        <v>45</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="n">
-        <v>488</v>
-      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="n">
-        <v>737</v>
+        <v>308.5249</v>
       </c>
       <c r="M33" t="n">
-        <v>375</v>
+        <v>133.09209</v>
       </c>
       <c r="N33" t="n">
-        <v>1600</v>
+        <v>279.9523</v>
       </c>
       <c r="O33" t="n">
-        <v>476</v>
+        <v>721.5692899999999</v>
       </c>
       <c r="P33" t="n">
-        <v>179</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>220</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>875</v>
+        <v>8</v>
       </c>
       <c r="S33" t="n">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U33" t="n">
-        <v>250</v>
+        <v>21.991661</v>
       </c>
       <c r="V33" t="n">
-        <v>312</v>
+        <v>0.28</v>
       </c>
       <c r="W33" t="n">
-        <v>1</v>
+        <v>24.11503283642837</v>
       </c>
       <c r="X33" t="n">
-        <v>28.4</v>
+        <v>22.94172005939238</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>95.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>659.9</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD33" t="n">
         <v>0</v>
@@ -4388,29 +4152,24 @@
         <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>196</v>
       </c>
       <c r="AK33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM33" t="inlineStr"/>
-      <c r="AN33" t="inlineStr"/>
+        <v>188</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>54829639</v>
+        <v>51629995</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -4418,65 +4177,79 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>88.5639972621492</v>
-      </c>
-      <c r="D34" t="inlineStr"/>
+        <v>77.03216974674881</v>
+      </c>
+      <c r="D34" t="n">
+        <v>20.2020202020202</v>
+      </c>
       <c r="E34" t="n">
-        <v>24.0054869684499</v>
-      </c>
-      <c r="F34" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>55</v>
+      </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34" t="n">
-        <v>61</v>
-      </c>
-      <c r="I34" t="inlineStr"/>
+        <v>95</v>
+      </c>
+      <c r="I34" t="n">
+        <v>161</v>
+      </c>
       <c r="J34" t="n">
-        <v>1</v>
-      </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="K34" t="n">
+        <v>356</v>
+      </c>
+      <c r="L34" t="n">
+        <v>95</v>
+      </c>
+      <c r="M34" t="n">
+        <v>147</v>
+      </c>
+      <c r="N34" t="n">
+        <v>100</v>
+      </c>
       <c r="O34" t="n">
-        <v>657</v>
+        <v>342</v>
       </c>
       <c r="P34" t="n">
-        <v>435</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1171</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>746</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>25.6</v>
       </c>
       <c r="V34" t="n">
-        <v>746</v>
+        <v>0.21</v>
       </c>
       <c r="W34" t="n">
-        <v>2</v>
+        <v>25.97408671259732</v>
       </c>
       <c r="X34" t="n">
-        <v>21.6</v>
+        <v>25.04391741993535</v>
       </c>
       <c r="Y34" t="n">
-        <v>0.36</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>78.2</v>
+        <v>1</v>
       </c>
       <c r="AA34" t="n">
-        <v>361.7</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
         <v>0</v>
@@ -4494,33 +4267,20 @@
         <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
       </c>
-      <c r="AJ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>124</v>
-      </c>
+      <c r="AJ34" t="inlineStr"/>
+      <c r="AK34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>54921492</v>
+        <v>51844056</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -4528,71 +4288,85 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>74.8008213552361</v>
-      </c>
-      <c r="D35" t="inlineStr"/>
+        <v>76.3613963039014</v>
+      </c>
+      <c r="D35" t="n">
+        <v>25.3934311203181</v>
+      </c>
       <c r="E35" t="n">
-        <v>30.5555555555556</v>
-      </c>
-      <c r="F35" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>55</v>
+      </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>55</v>
-      </c>
-      <c r="I35" t="inlineStr"/>
+        <v>1253</v>
+      </c>
+      <c r="I35" t="n">
+        <v>314</v>
+      </c>
       <c r="J35" t="n">
-        <v>1</v>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+        <v>560</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2127</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1253</v>
+      </c>
+      <c r="M35" t="n">
+        <v>298</v>
+      </c>
+      <c r="N35" t="n">
+        <v>536</v>
+      </c>
       <c r="O35" t="n">
-        <v>415</v>
+        <v>2087</v>
       </c>
       <c r="P35" t="n">
-        <v>713</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>289</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1417</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>28.4</v>
       </c>
       <c r="V35" t="n">
-        <v>12</v>
+        <v>0.26</v>
       </c>
       <c r="W35" t="n">
-        <v>1</v>
+        <v>28.32957987035737</v>
       </c>
       <c r="X35" t="n">
-        <v>24.6</v>
+        <v>27.29185104880338</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.36</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>82.7</v>
+        <v>1</v>
       </c>
       <c r="AA35" t="n">
-        <v>485.8</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
         <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
         <v>0</v>
@@ -4612,25 +4386,12 @@
       <c r="AI35" t="n">
         <v>0</v>
       </c>
-      <c r="AJ35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>188</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>140</v>
-      </c>
+      <c r="AJ35" t="inlineStr"/>
+      <c r="AK35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>53687854</v>
+        <v>54470472</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -4638,117 +4399,106 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>89.5003422313484</v>
-      </c>
-      <c r="D36" t="inlineStr"/>
+        <v>89.39630390143741</v>
+      </c>
+      <c r="D36" t="n">
+        <v>27.9903628117914</v>
+      </c>
       <c r="E36" t="n">
-        <v>21.875</v>
-      </c>
-      <c r="F36" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>41</v>
+      </c>
       <c r="G36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" t="n">
-        <v>43</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="n">
-        <v>299</v>
-      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
       <c r="L36" t="n">
-        <v>589</v>
+        <v>518</v>
       </c>
       <c r="M36" t="n">
-        <v>356</v>
+        <v>489</v>
       </c>
       <c r="N36" t="n">
-        <v>1174</v>
+        <v>349</v>
       </c>
       <c r="O36" t="n">
-        <v>201</v>
+        <v>1356</v>
       </c>
       <c r="P36" t="n">
-        <v>219</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>324</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>744</v>
+        <v>16</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>26.9</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="W36" t="n">
-        <v>2</v>
+        <v>28.17042492726548</v>
       </c>
       <c r="X36" t="n">
-        <v>27.4</v>
+        <v>27.5703465376642</v>
       </c>
       <c r="Y36" t="n">
-        <v>0.27</v>
+        <v>1</v>
       </c>
       <c r="Z36" t="n">
-        <v>86.5</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>556.3</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
         <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF36" t="n">
         <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="AK36" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>137</v>
+        <v>110</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>53798246</v>
+        <v>52552651</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -4756,76 +4506,80 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>74.0177960301164</v>
+        <v>77.63997262149211</v>
       </c>
       <c r="D37" t="n">
-        <v>1</v>
+        <v>25.8805706350208</v>
       </c>
       <c r="E37" t="n">
-        <v>33.3049886621315</v>
-      </c>
-      <c r="F37" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>55</v>
+      </c>
       <c r="G37" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" t="n">
-        <v>50</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="n">
-        <v>1</v>
-      </c>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+      <c r="L37" t="n">
+        <v>155.31346</v>
+      </c>
+      <c r="M37" t="n">
+        <v>60.364746</v>
+      </c>
+      <c r="N37" t="n">
+        <v>25.387777</v>
+      </c>
       <c r="O37" t="n">
-        <v>193</v>
+        <v>241.065983</v>
       </c>
       <c r="P37" t="n">
-        <v>201</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>284</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>678</v>
+        <v>45</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="T37" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>25.566442</v>
       </c>
       <c r="V37" t="n">
-        <v>5</v>
+        <v>0.26</v>
       </c>
       <c r="W37" t="n">
-        <v>1</v>
+        <v>24.95709935863556</v>
       </c>
       <c r="X37" t="n">
-        <v>27</v>
+        <v>24.34329842496372</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>88.8</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>588.2</v>
+        <v>1</v>
       </c>
       <c r="AB37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE37" t="n">
         <v>0</v>
@@ -4834,28 +4588,19 @@
         <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="AK37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>186</v>
-      </c>
-      <c r="AN37" t="n">
-        <v>130</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
